--- a/metrics/mobile-component-metrics-2026-02-28.xlsx
+++ b/metrics/mobile-component-metrics-2026-02-28.xlsx
@@ -316,7 +316,7 @@
     <t>HeaderCompactStandard</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/index.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/AesCryptoTestForm.tsx, repos/metamask-mobile/app/components/Views/AddAsset/AddAsset.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SelectComponent/index.js, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/Identity/BackupAndSyncSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/Contacts/index.js, repos/metamask-mobile/app/components/Views/Settings/AppInformation/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenList/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnInputView/EarnInputView.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/pay-with-modal/pay-with-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/estimates-modal/estimates-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-modal/gas-fee-token-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/expandable/expandable.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/WebviewModal/WebviewModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/index.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/AesCryptoTestForm.tsx, repos/metamask-mobile/app/components/Views/AddAsset/AddAsset.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/UI/SelectComponent/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/Identity/BackupAndSyncSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/Contacts/index.js, repos/metamask-mobile/app/components/Views/Settings/AppInformation/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenList/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnInputView/EarnInputView.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/pay-with-modal/pay-with-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/estimates-modal/estimates-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-modal/gas-fee-token-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/expandable/expandable.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/WebviewModal/WebviewModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx</t>
   </si>
   <si>
     <t>ConditionalScrollView</t>
@@ -346,7 +346,7 @@
     <t>repos/metamask-mobile/app/components/Views/Root/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.stories.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummaryTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx</t>
+    <t>repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummaryTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/Views/PickComponent/index.tsx, repos/metamask-mobile/app/components/Views/PickComponent/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx</t>
@@ -358,7 +358,7 @@
     <t>repos/metamask-mobile/app/components/Views/TradeWalletActions/TradeWalletActions.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/TokensFullView/TokensFullView.tsx, repos/metamask-mobile/app/components/Views/QRTabSwitcher/QRTabSwitcher.tsx, repos/metamask-mobile/app/components/Views/DeFiFullView/DeFiFullView.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/TokensFullView/TokensFullView.tsx, repos/metamask-mobile/app/components/Views/QRTabSwitcher/QRTabSwitcher.tsx, repos/metamask-mobile/app/components/Views/DeFiFullView/DeFiFullView.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx</t>
@@ -415,7 +415,7 @@
     <t>ButtonPill</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx</t>
   </si>
   <si>
     <t>ButtonHero</t>
@@ -430,13 +430,13 @@
     <t>repos/metamask-mobile/app/components/UI/AccountFromToInfoCard/AddressFrom.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/ApproveTransactionHeader/ApproveTransactionHeader.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/hooks/useOnboardingHeader.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInfoRow/SnapUIInfoRow.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInfoRow/SnapUIInfoRow.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddress/SnapUIAddress.tsx, repos/metamask-mobile/app/components/Snaps/SnapIcon/SnapIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SocialLoginIosUser/index.tsx, repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/RestoreWallet.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/RestoreWallet.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/QRScanner/index.tsx, repos/metamask-mobile/app/components/Views/QRScanner/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainTransactionsView/MultichainTransactionsFooter.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/Asset/ActivityHeader.tsx, repos/metamask-mobile/app/components/Views/AssetDetails/index.tsx, repos/metamask-mobile/app/components/Views/AssetDetails/index.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Clipboard.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/AesCryptoTestForm.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/AesCryptoTestForm.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountAction/AccountAction.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Transactions/TransactionsFooter.tsx, repos/metamask-mobile/app/components/UI/TemplateRenderer/TemplateRenderer.tsx, repos/metamask-mobile/app/components/UI/TemplateRenderer/TemplateRenderer.tsx, repos/metamask-mobile/app/components/UI/SrpWordSuggestions/index.tsx, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SecurityOptionToggle/SecurityOptionToggle.tsx, repos/metamask-mobile/app/components/UI/SecurityOptionToggle/SecurityOptionToggle.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionDetails.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/ContextualNetworkPicker/ContextualNetworkPicker.tsx, repos/metamask-mobile/app/components/UI/ConnectHeader/index.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/AccountOverview/index.js, repos/metamask-mobile/app/components/UI/AccountOverview/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountFromToInfoCard/AddressFrom.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Base/TokenIcon/index.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/Base/Title/Title.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/sectionHeader.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/sectionHeader.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/PushNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/DisplayNFTMediaSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DisplayNFTMediaSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/BatchAccountBalanceSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/BatchAccountBalanceSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectTokensSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectTokensSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectNFTSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectNFTSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/DefaultSettings/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/DefaultSettings/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/ConnectHardware/SelectHardware/index.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectCreateInitialAccount/AccountConnectCreateInitialAccount.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/shared/StockBadge/StockBadge.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/FiatDisplay/FiatDisplay.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/FiatDisplay/FiatDisplay.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/AssetPill/AssetPill.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/BalanceChangeRow/BalanceChangeRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Earn/components/CurrencySwitch.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/AvatarGroup.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsListItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsListItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/ChartNavigationButton/ChartNavigationButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/usePendingTransactionAlert.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/useAccountTypeUpgrade.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/useAccountTypeUpgrade.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/title/title.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/title/title.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/smart-contract-with-logo/smart-contract-with-logo.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nested-transaction-data/nested-transaction-data.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/hero-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/hero-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/batched-transactions-tag/batched-transactions-tag.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBannerLink.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissions/SnapPermissions.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapVersionTag/SnapVersionTag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/CustomNotificationsRow/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/RpcUrlInput.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/ResetAccountModal/ResetAccountModal.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/ResetAccountModal/ResetAccountModal.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Title/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Title/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/StakingProviderField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/StakingProviderField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcUrlInput.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenLogo/TrendingTokenLogo.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakeButton/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsReferralCodeTag/RewardsReferralCodeTag.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAmountDisplay/PredictAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWatchlistMarkets/PerpsWatchlistMarkets.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionItem/PerpsTransactionItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionItem/PerpsTransactionItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionDetailAssetHero/PerpsTransactionDetailAssetHero.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTokenLogo/PerpsTokenLogo.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsSlider/PerpsSlider.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsSlider/PerpsSlider.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPriceDeviationWarning/PerpsPriceDeviationWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOICapWarning/PerpsOICapWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTypeSection/PerpsMarketTypeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketList/PerpsMarketList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketCategoryBadge/PerpsMarketCategoryBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoader/PerpsLoader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverage/PerpsLeverage.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFeesDisplay/PerpsFeesDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFeesDisplay/PerpsFeesDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFillTag/PerpsFillTag.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsTestnetToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsTestnetToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsProviderToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsProviderToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlestickChartIntervalSelector/PerpsCandlestickChartIntervalSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBadge/PerpsBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/FundingCountdown/FundingCountdown.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/UnstakeBanner.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingWithdrawalConfirmationView/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BridgeActivityItemTxSegments.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BridgeStepDescription.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteCountdownTimer/QuoteCountdownTimer.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/MarketDetailsList/MarketDetailsList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/total-row/total-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/receive-row/receive-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/percentage-row/percentage-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-time-row/bridge-time-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-withdraw-balance/predict-withdraw-balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/selected-gas-fee-token/selected-gas-fee-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/priority-fee-input/priority-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/priority-fee-input/priority-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/max-base-fee-input/max-base-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/max-base-fee-input/max-base-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-price-input/gas-price-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-speed/gas-speed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-modal-header/gas-modal-header.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-total-row/transaction-details-total-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/alerts/alert-message/alert-message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-row/transaction-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-paid-with-row/transaction-details-paid-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-date-row/transaction-details-date-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-date-row/transaction-details-date-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-network-fee-row/transaction-details-network-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-hero/transaction-details-hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-bridge-fee-row/transaction-details-bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-account-row/transaction-details-account-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/pill/pill.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-section-accordion/info-section-accordion.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/components/AddAccountItem.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/AutoLock/AutoLock.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/AutoLock/AutoLock.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccount/SmartAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/TruncatedError/TruncatedError.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/SdkErrorAlert/SdkErrorAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositPhoneField/DepositPhoneField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositPhoneField/DepositPhoneField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProcessingInfoModal/ProcessingInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/TPSLCountWarningTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/ConvertTokenRow/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/ConvertTokenRow/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/ConvertTokenRow/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/ConvertTokenRow/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-details/staking-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-details/staking-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-row/network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/info-section-origin-and-details/info-section-origin-and-details.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/LegalLinks/LegalLinks.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/LegalLinks/LegalLinks.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/UnstakeBanner/UnstakeBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/ChartTimespanButtonGroup/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/GraphTooltip/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/GraphTooltip/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsTimePeriod/EarningsTimePeriod.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsTimePeriod/EarningsTimePeriod.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/components/MusdBalanceCard/MusdBalanceCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/components/MusdBalanceCard/MusdBalanceCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/components/MusdBalanceCard/MusdBalanceCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryChart/EarningsHistoryChart.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryChart/EarningsHistoryChart.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/typed-sign-decoded/typed-sign-decoded.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/info-date/info-date.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/network/network.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx</t>
+    <t>repos/metamask-mobile/app/components/hooks/useOnboardingHeader.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInfoRow/SnapUIInfoRow.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInfoRow/SnapUIInfoRow.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddress/SnapUIAddress.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapIcon/SnapIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SocialLoginIosUser/index.tsx, repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/RestoreWallet.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/RestoreWallet.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/QRScanner/index.tsx, repos/metamask-mobile/app/components/Views/QRScanner/index.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainTransactionsView/MultichainTransactionsFooter.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AssetDetails/index.tsx, repos/metamask-mobile/app/components/Views/AssetDetails/index.tsx, repos/metamask-mobile/app/components/Views/Asset/ActivityHeader.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Clipboard.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/AesCryptoTestForm.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/AesCryptoTestForm.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/Views/AccountAction/AccountAction.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Transactions/TransactionsFooter.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/TemplateRenderer/TemplateRenderer.tsx, repos/metamask-mobile/app/components/UI/TemplateRenderer/TemplateRenderer.tsx, repos/metamask-mobile/app/components/UI/SrpWordSuggestions/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SecurityOptionToggle/SecurityOptionToggle.tsx, repos/metamask-mobile/app/components/UI/SecurityOptionToggle/SecurityOptionToggle.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionDetails.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/ContextualNetworkPicker/ContextualNetworkPicker.tsx, repos/metamask-mobile/app/components/UI/ConnectHeader/index.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AccountOverview/index.js, repos/metamask-mobile/app/components/UI/AccountOverview/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountFromToInfoCard/AddressFrom.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/Base/TokenIcon/index.tsx, repos/metamask-mobile/app/components/Base/Title/Title.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/sectionHeader.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/sectionHeader.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/PushNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DisplayNFTMediaSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DisplayNFTMediaSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/BatchAccountBalanceSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/BatchAccountBalanceSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectTokensSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectTokensSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectNFTSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectNFTSettings/index.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/DefaultSettings/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/DefaultSettings/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/ConnectHardware/SelectHardware/index.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectCreateInitialAccount/AccountConnectCreateInitialAccount.tsx, repos/metamask-mobile/app/components/UI/shared/StockBadge/StockBadge.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/FiatDisplay/FiatDisplay.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/FiatDisplay/FiatDisplay.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/BalanceChangeRow/BalanceChangeRow.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/AssetPill/AssetPill.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Earn/components/CurrencySwitch.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/AvatarGroup.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsListItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsListItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/ChartNavigationButton/ChartNavigationButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/usePendingTransactionAlert.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/useAccountTypeUpgrade.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/useAccountTypeUpgrade.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/title/title.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/title/title.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/smart-contract-with-logo/smart-contract-with-logo.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nested-transaction-data/nested-transaction-data.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/hero-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/hero-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBannerLink.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/batched-transactions-tag/batched-transactions-tag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapVersionTag/SnapVersionTag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissions/SnapPermissions.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/RpcUrlInput.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/CustomNotificationsRow/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/ResetAccountModal/ResetAccountModal.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/ResetAccountModal/ResetAccountModal.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Title/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Title/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/StakingProviderField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/StakingProviderField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcUrlInput.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenLogo/TrendingTokenLogo.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakeButton/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsReferralCodeTag/RewardsReferralCodeTag.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAmountDisplay/PredictAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWatchlistMarkets/PerpsWatchlistMarkets.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionItem/PerpsTransactionItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionItem/PerpsTransactionItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionDetailAssetHero/PerpsTransactionDetailAssetHero.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTokenLogo/PerpsTokenLogo.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsSlider/PerpsSlider.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsSlider/PerpsSlider.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPriceDeviationWarning/PerpsPriceDeviationWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOICapWarning/PerpsOICapWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTypeSection/PerpsMarketTypeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketList/PerpsMarketList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketCategoryBadge/PerpsMarketCategoryBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoader/PerpsLoader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverage/PerpsLeverage.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFeesDisplay/PerpsFeesDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFeesDisplay/PerpsFeesDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFillTag/PerpsFillTag.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsTestnetToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsTestnetToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsProviderToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsProviderToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlestickChartIntervalSelector/PerpsCandlestickChartIntervalSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBadge/PerpsBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/FundingCountdown/FundingCountdown.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/UnstakeBanner.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingWithdrawalConfirmationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BridgeStepDescription.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BridgeActivityItemTxSegments.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteCountdownTimer/QuoteCountdownTimer.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/MarketDetailsList/MarketDetailsList.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/receive-row/receive-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/total-row/total-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/percentage-row/percentage-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-time-row/bridge-time-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-withdraw-balance/predict-withdraw-balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/selected-gas-fee-token/selected-gas-fee-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/priority-fee-input/priority-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/priority-fee-input/priority-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/max-base-fee-input/max-base-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/max-base-fee-input/max-base-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-speed/gas-speed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-price-input/gas-price-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-modal-header/gas-modal-header.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/alerts/alert-message/alert-message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-total-row/transaction-details-total-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-row/transaction-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-paid-with-row/transaction-details-paid-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-network-fee-row/transaction-details-network-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-hero/transaction-details-hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-account-row/transaction-details-account-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-date-row/transaction-details-date-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-date-row/transaction-details-date-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-bridge-fee-row/transaction-details-bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/pill/pill.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-section-accordion/info-section-accordion.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/AutoLock/AutoLock.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/AutoLock/AutoLock.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/components/AddAccountItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccount/SmartAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/TruncatedError/TruncatedError.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/SdkErrorAlert/SdkErrorAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositPhoneField/DepositPhoneField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositPhoneField/DepositPhoneField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProcessingInfoModal/ProcessingInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/TPSLCountWarningTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/ConvertTokenRow/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/ConvertTokenRow/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/ConvertTokenRow/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/ConvertTokenRow/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-details/staking-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-details/staking-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-row/network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/info-section-origin-and-details/info-section-origin-and-details.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/LegalLinks/LegalLinks.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/LegalLinks/LegalLinks.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/UnstakeBanner/UnstakeBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/GraphTooltip/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/GraphTooltip/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/ChartTimespanButtonGroup/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsTimePeriod/EarningsTimePeriod.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsTimePeriod/EarningsTimePeriod.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryChart/EarningsHistoryChart.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryChart/EarningsHistoryChart.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/components/MusdBalanceCard/MusdBalanceCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/components/MusdBalanceCard/MusdBalanceCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/components/MusdBalanceCard/MusdBalanceCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/typed-sign-decoded/typed-sign-decoded.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/network/network.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/info-date/info-date.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx</t>
   </si>
   <si>
     <t>SensitiveText</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionDetails.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/CaipAccountSelectorList/CaipAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/AssetElement/index.tsx, repos/metamask-mobile/app/components/UI/AssetElement/index.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Assets/components/BalanceChange/AccountGroupBalanceChange.tsx, repos/metamask-mobile/app/components/UI/Assets/components/BalanceChange/AccountGroupBalanceChange.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx</t>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionDetails.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/CaipAccountSelectorList/CaipAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/AssetElement/index.tsx, repos/metamask-mobile/app/components/UI/AssetElement/index.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Assets/components/BalanceChange/AccountGroupBalanceChange.tsx, repos/metamask-mobile/app/components/UI/Assets/components/BalanceChange/AccountGroupBalanceChange.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx</t>
   </si>
   <si>
     <t>TagUrl</t>
@@ -448,13 +448,13 @@
     <t>Tag</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/index.tsx</t>
+    <t>repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/index.tsx</t>
   </si>
   <si>
     <t>SheetHeader</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/SelectSRP/SelectSRPBottomSheet.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingleSelector/AccountConnectSingleSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealPrivateKey/RevealPrivateKey.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/SelectSRP/SelectSRPBottomSheet.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingleSelector/AccountConnectSingleSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealPrivateKey/RevealPrivateKey.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx</t>
   </si>
   <si>
     <t>SelectButton</t>
@@ -472,7 +472,7 @@
     <t>ListItemSelect</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx</t>
   </si>
   <si>
     <t>ListItemMultiSelect</t>
@@ -484,16 +484,16 @@
     <t>ListItemColumn</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/ListItemColumnEnd.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx</t>
+    <t>repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/ListItemColumnEnd.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx</t>
   </si>
   <si>
     <t>ListItem</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/CustomAction/CustomAction.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Base/SelectorButton.tsx, repos/metamask-mobile/app/components/Snaps/SnapUILink/SnapUILink.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIIcon/SnapUIIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICopyable/SnapUICopyable.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICopyable/SnapUICopyable.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AccountAction/AccountAction.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SDKFeedback/index.tsx, repos/metamask-mobile/app/components/UI/QRHardware/AnimatedQRScanner.tsx, repos/metamask-mobile/app/components/UI/QRHardware/AnimatedQRScanner.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/MaliciousDappIndicators.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/MaliciousDappIndicators.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/ButtonReveal/index.tsx, repos/metamask-mobile/app/components/UI/ButtonReveal/index.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/index.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/shared/StockBadge/StockBadge.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useEarnToasts.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useEarnToasts.tsx, repos/metamask-mobile/app/components/UI/Earn/components/CurrencySwitch.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-spending-cap-button/edit-spending-cap-button.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/batched-transactions-tag/batched-transactions-tag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapVersionTag/SnapVersionTag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapElement/SnapElement.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/CustomNotificationsRow/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardPointsAnimation/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPriceDeviationWarning/PerpsPriceDeviationWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOICapWarning/PerpsOICapWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTypeSection/PerpsMarketTypeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketCategoryBadge/PerpsMarketCategoryBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/StepProgressBarItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/PulsingCircle.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/FlipQuoteButton/index.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/selected-gas-fee-token/selected-gas-fee-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/inline-alert/inline-alert.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-section-accordion/info-section-accordion.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/components/AddAccountItem.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccount/SmartAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositDateField/DepositDateField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/copy-icon/copy-icon.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx</t>
+    <t>repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/CustomAction/CustomAction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Base/SelectorButton.tsx, repos/metamask-mobile/app/components/Snaps/SnapUILink/SnapUILink.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIIcon/SnapUIIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICopyable/SnapUICopyable.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICopyable/SnapUICopyable.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/Views/AccountAction/AccountAction.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SDKFeedback/index.tsx, repos/metamask-mobile/app/components/UI/QRHardware/AnimatedQRScanner.tsx, repos/metamask-mobile/app/components/UI/QRHardware/AnimatedQRScanner.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/MaliciousDappIndicators.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/MaliciousDappIndicators.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/ButtonReveal/index.tsx, repos/metamask-mobile/app/components/UI/ButtonReveal/index.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/index.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/UI/shared/StockBadge/StockBadge.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Earn/components/CurrencySwitch.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useEarnToasts.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useEarnToasts.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-spending-cap-button/edit-spending-cap-button.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/batched-transactions-tag/batched-transactions-tag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapVersionTag/SnapVersionTag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapElement/SnapElement.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/CustomNotificationsRow/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardPointsAnimation/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPriceDeviationWarning/PerpsPriceDeviationWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOICapWarning/PerpsOICapWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTypeSection/PerpsMarketTypeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketCategoryBadge/PerpsMarketCategoryBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/StepProgressBarItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/PulsingCircle.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/FlipQuoteButton/index.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/selected-gas-fee-token/selected-gas-fee-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-section-accordion/info-section-accordion.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/inline-alert/inline-alert.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/components/AddAccountItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccount/SmartAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositDateField/DepositDateField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/copy-icon/copy-icon.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx</t>
   </si>
   <si>
     <t>TextFieldSearch</t>
@@ -502,46 +502,46 @@
     <t>repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Box.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx</t>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Box.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx</t>
   </si>
   <si>
     <t>HelpText</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx</t>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx</t>
   </si>
   <si>
     <t>Cell</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/UI/NetworkSelectorList/NetworkSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelector/NetworkMultiSelector.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/CaipAccountSelectorList/CaipAccountSelectorList.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapElement/SnapElement.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/UI/NetworkSelectorList/NetworkSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelector/NetworkMultiSelector.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/CaipAccountSelectorList/CaipAccountSelectorList.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapElement/SnapElement.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/UnstakeTimeCard/UnstakeTimeCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/hooks/useOnboardingHeader.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/TokensFullView/TokensFullView.tsx, repos/metamask-mobile/app/components/Views/QRTabSwitcher/QRTabSwitcher.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/DeFiFullView/DeFiFullView.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/UI/shared/BaseControlBar/BaseControlBar.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenListControlBar/TokenListControlBar.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/flat-nav-header/flat-nav-header.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/ContactForm/index.js, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsChartFullscreenModal/PerpsChartFullscreenModal.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/ApprovalText/ApprovalTooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/predict-claim-info/predict-claim-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-modal-header/gas-modal-header.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/navbar/navbar.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/copy-button/copy-button.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/ScamWarningIcon/ScamWarningIcon.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SocialLoginIosUser/index.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainTransactionsView/MultichainTransactionsFooter.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Transactions/TransactionsFooter.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SheetActionView/SheetActionVIew.tsx, repos/metamask-mobile/app/components/UI/SheetActionView/SheetActionVIew.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/PhishingModal/index.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/CollectibleMedia/CollectibleMedia.tsx, repos/metamask-mobile/app/components/UI/ActionView/index.js, repos/metamask-mobile/app/components/UI/ActionView/index.js, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/ResetNotificationsButton.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-amount-keyboard/edit-amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-amount-keyboard/edit-amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/AmbiguousAddressSheet/AmbiguousAddressSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Footers/AnnouncementCtaFooter.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Footers/BlockExplorerFooter.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/QuickAmounts.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsConnectionErrorButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsHIP3DebugButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/EarnWithdrawInputView.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/EarnWithdrawInputView.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnInputView/EarnInputView.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SwapsKeypad/QuickPickButtons.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SwapsConfirmButton/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/advanced-gas-price-modal/advanced-gas-price-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/advanced-eip1559-modal/advanced-eip1559-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-retry/transaction-details-retry.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/RemoveAccount/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingButtons/StakingButtons.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingButtons/StakingButtons.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OrderProcessing/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OrderProcessing/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProcessingInfoModal/ProcessingInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/CustomAction/CustomAction.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistoryButton/EarningsHistoryButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount-keyboard/amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx</t>
+    <t>repos/metamask-mobile/app/components/hooks/useOnboardingHeader.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/TokensFullView/TokensFullView.tsx, repos/metamask-mobile/app/components/Views/QRTabSwitcher/QRTabSwitcher.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/DeFiFullView/DeFiFullView.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/UI/shared/BaseControlBar/BaseControlBar.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenListControlBar/TokenListControlBar.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/flat-nav-header/flat-nav-header.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/ContactForm/index.js, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsChartFullscreenModal/PerpsChartFullscreenModal.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/ApprovalText/ApprovalTooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/predict-claim-info/predict-claim-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-modal-header/gas-modal-header.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/navbar/navbar.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/copy-button/copy-button.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/ScamWarningIcon/ScamWarningIcon.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SocialLoginIosUser/index.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainTransactionsView/MultichainTransactionsFooter.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Transactions/TransactionsFooter.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SheetActionView/SheetActionVIew.tsx, repos/metamask-mobile/app/components/UI/SheetActionView/SheetActionVIew.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/PhishingModal/index.js, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/CollectibleMedia/CollectibleMedia.tsx, repos/metamask-mobile/app/components/UI/ActionView/index.js, repos/metamask-mobile/app/components/UI/ActionView/index.js, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/ResetNotificationsButton.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-amount-keyboard/edit-amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-amount-keyboard/edit-amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/Contacts/AmbiguousAddressSheet/AmbiguousAddressSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Footers/AnnouncementCtaFooter.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Footers/BlockExplorerFooter.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/QuickAmounts.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsHIP3DebugButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsConnectionErrorButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/EarnWithdrawInputView.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/EarnWithdrawInputView.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnInputView/EarnInputView.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SwapsConfirmButton/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SwapsKeypad/QuickPickButtons.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/advanced-eip1559-modal/advanced-eip1559-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/advanced-gas-price-modal/advanced-gas-price-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-retry/transaction-details-retry.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/RemoveAccount/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingButtons/StakingButtons.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingButtons/StakingButtons.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OrderProcessing/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OrderProcessing/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProcessingInfoModal/ProcessingInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/CustomAction/CustomAction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistoryButton/EarningsHistoryButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount-keyboard/amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx</t>
   </si>
   <si>
     <t>BottomSheetHeader</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUITooltip/SnapUITooltip.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NftFullView/NftFullView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/SelectOptionSheet/OptionsSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeNetworkSelectorBase.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/MultichainAccountActions/MultichainAccountActions.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/RecipientSelectorModal/RecipientSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/SettingsModal/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProcessingInfoModal/ProcessingInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ConfigurationModal/ConfigurationModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Modals/Settings/SettingsModal.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapDialogApproval/SnapDialogApproval.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/Views/TokenDetails.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/Approval/TemplateConfirmation/TemplateConfirmation.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx</t>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUITooltip/SnapUITooltip.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NftFullView/NftFullView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/SelectOptionSheet/OptionsSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeNetworkSelectorBase.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/MultichainAccountActions/MultichainAccountActions.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/RecipientSelectorModal/RecipientSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/SettingsModal/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProcessingInfoModal/ProcessingInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ConfigurationModal/ConfigurationModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Modals/Settings/SettingsModal.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapDialogApproval/SnapDialogApproval.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/Views/TokenDetails.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/Approval/TemplateConfirmation/TemplateConfirmation.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx</t>
   </si>
   <si>
     <t>BottomSheet</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/WalletActions/WalletActions.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/SelectSRP/SelectSRPBottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/index.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccountBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissions.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnect.tsx, repos/metamask-mobile/app/components/Views/AccountActions/AccountActions.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SelectOptionSheet/OptionsSheet.tsx, repos/metamask-mobile/app/components/UI/QRHardware/QRSigningTransactionModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/FundActionMenu/FundActionMenu.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/Approvals/AddChainApproval/AddChainApproval.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKLoadingModal/SDKLoadingModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKFeedbackModal/SDKFeedbackModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/EditNetworkMenu.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/MoreTokenActionsMenu.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Notification/ResetNotificationsModal/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Identity/ConfirmTurnOnBackupAndSyncModal/ConfirmTurnOnBackupAndSyncModal.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeNetworkSelectorBase.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/confirm/confirm-component.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/AmbiguousAddressSheet/AmbiguousAddressSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/MultichainAccountActions/MultichainAccountActions.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenList/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/RecipientSelectorModal/RecipientSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/pay-with-modal/pay-with-modal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/SettingsModal/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProcessingInfoModal/ProcessingInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/WebviewModal/WebviewModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ConfigurationModal/ConfigurationModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Modals/Settings/SettingsModal.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/WalletActions/WalletActions.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/SelectSRP/SelectSRPBottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/index.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccountBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissions.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnect.tsx, repos/metamask-mobile/app/components/Views/AccountActions/AccountActions.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SelectOptionSheet/OptionsSheet.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/QRHardware/QRSigningTransactionModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/FundActionMenu/FundActionMenu.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/Approvals/AddChainApproval/AddChainApproval.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKLoadingModal/SDKLoadingModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKFeedbackModal/SDKFeedbackModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/EditNetworkMenu.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/MoreTokenActionsMenu.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Notification/ResetNotificationsModal/index.tsx, repos/metamask-mobile/app/components/UI/Identity/ConfirmTurnOnBackupAndSyncModal/ConfirmTurnOnBackupAndSyncModal.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeNetworkSelectorBase.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/confirm/confirm-component.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/AmbiguousAddressSheet/AmbiguousAddressSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/MultichainAccountActions/MultichainAccountActions.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenList/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/RecipientSelectorModal/RecipientSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/pay-with-modal/pay-with-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/SettingsModal/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProcessingInfoModal/ProcessingInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/WebviewModal/WebviewModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ConfigurationModal/ConfigurationModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Modals/Settings/SettingsModal.tsx</t>
   </si>
   <si>
     <t>Banner</t>
@@ -550,13 +550,13 @@
     <t>repos/metamask-mobile/app/components/Snaps/SnapUIBanner/SnapUIBanner.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/CollectibleDetectionModal/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnMaintenanceBanner/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/UnstakeBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/UnstakeBanner/UnstakeBanner.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/index.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionListItem/MultichainTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/MultichainBridgeTransactionListItem/MultichainBridgeTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Base/RemoteImage/RemoteImageBadgeWrapper.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/components/Token.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Icon.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-icon/token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Headers/NFTImageHeader.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardAssetItem/CardAssetItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/ConvertTokenRow/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/components/MusdBalanceCard/MusdBalanceCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx</t>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/index.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/MultichainBridgeTransactionListItem/MultichainBridgeTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionListItem/MultichainTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Base/RemoteImage/RemoteImageBadgeWrapper.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/components/Token.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Icon.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-icon/token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Headers/NFTImageHeader.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardAssetItem/CardAssetItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/ConvertTokenRow/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/components/MusdBalanceCard/MusdBalanceCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx</t>
   </si>
   <si>
     <t>Badge</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/index.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionListItem/MultichainTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/MultichainBridgeTransactionListItem/MultichainBridgeTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Base/RemoteImage/RemoteImageBadgeWrapper.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/components/Token.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-icon/token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Headers/NFTImageHeader.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingWithdrawalConfirmationView/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardAssetItem/CardAssetItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/ConvertTokenRow/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/components/MusdBalanceCard/MusdBalanceCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx</t>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/index.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainBridgeTransactionListItem/MultichainBridgeTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionListItem/MultichainTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Base/RemoteImage/RemoteImageBadgeWrapper.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/components/Token.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-icon/token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Headers/NFTImageHeader.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingWithdrawalConfirmationView/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardAssetItem/CardAssetItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/ConvertTokenRow/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/MusdQuickConvertView/components/MusdBalanceCard/MusdBalanceCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/AccountNetworkIndicator/AccountNetworkIndicator.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx</t>
@@ -565,13 +565,13 @@
     <t>Avatar</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/NetworkInfo/index.tsx, repos/metamask-mobile/app/components/UI/ContextualNetworkPicker/ContextualNetworkPicker.tsx, repos/metamask-mobile/app/components/UI/AccountRightButton/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/UI/shared/BaseControlBar/BaseControlBar.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/AvatarGroup.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/ContactForm/index.js, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountTag/AccountTag.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/network/network.tsx</t>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/NetworkInfo/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/ContextualNetworkPicker/ContextualNetworkPicker.tsx, repos/metamask-mobile/app/components/UI/AccountRightButton/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/UI/shared/BaseControlBar/BaseControlBar.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/AvatarGroup.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/ContactForm/index.js, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountTag/AccountTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/network/network.tsx</t>
   </si>
   <si>
     <t>Accordion</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx</t>
+    <t>repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx</t>
   </si>
   <si>
     <t>AccountListHeader</t>
@@ -589,10 +589,10 @@
     <t>repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/index.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectCreateInitialAccount/AccountConnectCreateInitialAccount.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/usePendingTransactionAlert.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectCreateInitialAccount/AccountConnectCreateInitialAccount.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/usePendingTransactionAlert.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx</t>
@@ -619,19 +619,19 @@
     <t>repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnNetworkAvatar/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Assets/components/AssetLogo/AssetLogo.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/AssetPill/AssetPill.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-row/network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/info-section-origin-and-details/info-section-origin-and-details.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx</t>
+    <t>repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnNetworkAvatar/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Assets/components/AssetLogo/AssetLogo.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/AssetPill/AssetPill.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-row/network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/info-section-origin-and-details/info-section-origin-and-details.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapIcon/SnapIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx</t>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapIcon/SnapIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/Snaps/SnapUIAvatar/SnapUIAvatar.tsx, repos/metamask-mobile/app/components/UI/Identicon/index.tsx, repos/metamask-mobile/app/components/UI/AccountRightButton/index.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx</t>
@@ -643,7 +643,7 @@
     <t>repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx</t>
+    <t>repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx</t>
   </si>
   <si>
     <t>BadgeCount</t>
@@ -673,10 +673,10 @@
     <t>Box</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/sections.config.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NftFullView/NftFullView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/Homepage/Homepage.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/DeFiFullView/DeFiFullView.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/BrowserTab.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/BrowserTab.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/index.tsx, repos/metamask-mobile/app/components/UI/Tokens/index.tsx, repos/metamask-mobile/app/components/UI/Tokens/index.tsx, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGridItem.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelector/NetworkMultiSelector.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/FundActionMenu/FundActionMenu.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/BrowserBottomBar/index.tsx, repos/metamask-mobile/app/components/UI/BrowserBottomBar/index.tsx, repos/metamask-mobile/app/components/UI/BrowserBottomBar/index.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.stories.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/Keypad.stories.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/EditNetworkMenu.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/CollapsibleSectionHeader.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.stories.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/MoreTokenActionsMenu.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsSettingsView.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Predict/hooks/usePredictToastRegistrations.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderRedirect.tsx, repos/metamask-mobile/app/components/UI/OnboardingAnimation/__mocks__/OnboardingAnimation.tsx, repos/metamask-mobile/app/components/UI/Notification/List/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/FoxAnimation/__mocks__/FoxAnimation.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/ResourceRing.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/ResourceRing.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-list/token-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nft-list/nft-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nft-list/nft-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/SectionHeader/SectionHeader.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchResults/ExploreSearchResults.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchResults/ExploreSearchResults.tsx, repos/metamask-mobile/app/components/Views/TrendingView/Views/ExploreSearchScreen/ExploreSearchScreen.tsx, repos/metamask-mobile/app/components/Views/TrendingView/Views/ExploreSearchScreen/ExploreSearchScreen.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeviceSecurityToggle.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/SelectField.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/SelectField.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.stories.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionCard/SectionCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionRow/SectionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/TokensSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Perpetuals/PerpsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Perpetuals/PerpsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/DeFi/DeFiSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/DeFi/DeFiSection.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ThemeImageComponent/RewardsThemeImageComponent.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ThemeImageComponent/RewardsThemeImageComponent.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/RewardsActivity.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralInfoSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralActionsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummaryTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep2.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep3.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep1.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportTeamGradient/PredictSportTeamGradient.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicks.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCardWrapper.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAmountDisplay/PredictAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAmountDisplay/PredictAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictActionButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictActionButtons.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProgressBar/PerpsProgressBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SelectField.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyingVeriffKYC.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteCountdownTimer/QuoteCountdownTimer.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCarrousel.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCarrousel.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCarrousel.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/ViewMoreCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Perpetuals/components/PerpsViewMoreCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Root/Root.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProcessingInfoModal/ProcessingInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProcessingInfoModal/ProcessingInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrdersList/OrdersList.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrdersList/OrdersList.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabContent.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabContent.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/ReferralStatsSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabBar/PredictMarketDetailsTabBar.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabBar/PredictMarketDetailsTabBar.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsPositions/PredictMarketDetailsPositions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsPositions/PredictMarketDetailsPositions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Cta.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-list/token-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nft-list/nft-list.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeviceSecurityToggle.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralActionsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AddRewardsAccount/AddRewardsAccount.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/QuickAmounts/QuickAmounts.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictClaimButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHomeView/PerpsHomeView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHomeView/PerpsHomeView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/DaimoPayModal/DaimoPayModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/DaimoPayModal/DaimoPayModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/ConvertTokenRow/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx</t>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Views/TrendingView/sections.config.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NftFullView/NftFullView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/Homepage/Homepage.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/DeFiFullView/DeFiFullView.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/BrowserTab.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/BrowserTab.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/index.tsx, repos/metamask-mobile/app/components/UI/Tokens/index.tsx, repos/metamask-mobile/app/components/UI/Tokens/index.tsx, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGridItem.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelector/NetworkMultiSelector.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/FundActionMenu/FundActionMenu.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/BrowserBottomBar/index.tsx, repos/metamask-mobile/app/components/UI/BrowserBottomBar/index.tsx, repos/metamask-mobile/app/components/UI/BrowserBottomBar/index.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.stories.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/Keypad.stories.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/CollapsibleSectionHeader.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/EditNetworkMenu.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.stories.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/MoreTokenActionsMenu.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsSettingsView.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Predict/hooks/usePredictToastRegistrations.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderRedirect.tsx, repos/metamask-mobile/app/components/UI/OnboardingAnimation/__mocks__/OnboardingAnimation.tsx, repos/metamask-mobile/app/components/UI/Notification/List/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/FoxAnimation/__mocks__/FoxAnimation.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/ResourceRing.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/ResourceRing.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-list/token-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nft-list/nft-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nft-list/nft-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/SectionHeader/SectionHeader.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/Views/ExploreSearchScreen/ExploreSearchScreen.tsx, repos/metamask-mobile/app/components/Views/TrendingView/Views/ExploreSearchScreen/ExploreSearchScreen.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchResults/ExploreSearchResults.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchResults/ExploreSearchResults.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeviceSecurityToggle.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/SelectField.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/SelectField.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.stories.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionRow/SectionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionCard/SectionCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/TokensSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Perpetuals/PerpsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Perpetuals/PerpsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/DeFi/DeFiSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/DeFi/DeFiSection.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ThemeImageComponent/RewardsThemeImageComponent.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ThemeImageComponent/RewardsThemeImageComponent.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/RewardsActivity.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep2.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep3.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep1.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummaryTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralInfoSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralActionsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportTeamGradient/PredictSportTeamGradient.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicks.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCardWrapper.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAmountDisplay/PredictAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAmountDisplay/PredictAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictActionButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictActionButtons.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProgressBar/PerpsProgressBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyingVeriffKYC.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SelectField.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteCountdownTimer/QuoteCountdownTimer.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCarrousel.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCarrousel.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCarrousel.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/ViewMoreCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Perpetuals/components/PerpsViewMoreCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Root/Root.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProcessingInfoModal/ProcessingInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProcessingInfoModal/ProcessingInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrdersList/OrdersList.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrdersList/OrdersList.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabContent.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabContent.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/ReferralStatsSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabBar/PredictMarketDetailsTabBar.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabBar/PredictMarketDetailsTabBar.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsPositions/PredictMarketDetailsPositions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsPositions/PredictMarketDetailsPositions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Cta.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-list/token-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nft-list/nft-list.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeviceSecurityToggle.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralActionsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AddRewardsAccount/AddRewardsAccount.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/QuickAmounts/QuickAmounts.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictClaimButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHomeView/PerpsHomeView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHomeView/PerpsHomeView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/DaimoPayModal/DaimoPayModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/DaimoPayModal/DaimoPayModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/ConvertTokenRow/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx</t>
   </si>
   <si>
     <t>ButtonAnimated</t>
@@ -688,7 +688,7 @@
     <t>repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/BrowserTab.tsx, repos/metamask-mobile/app/components/Views/AssetDetails/index.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/DeviceAuthenticationButton/DeviceAuthenticationButton.tsx, repos/metamask-mobile/app/components/UI/AddressCopy/AddressCopy.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Card/routes/index.tsx, repos/metamask-mobile/app/components/UI/Card/routes/index.tsx, repos/metamask-mobile/app/components/UI/Card/routes/index.tsx, repos/metamask-mobile/app/components/UI/Card/routes/index.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardButton/CardButton.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/ConvertTokenRow/index.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/SelectOptionSheet/SelectOptionSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/CollapsibleSectionHeader.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/hooks/useRewardDashboardModals.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/ResourceRing.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/SectionHeader/SectionHeader.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/SelectField.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ThemeImageComponent/RewardsThemeImageComponent.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SelectField.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/InputStepperDescriptionRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/SelectOptionSheet/SelectOptionSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/CollapsibleSectionHeader.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/hooks/useRewardDashboardModals.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/ResourceRing.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/SectionHeader/SectionHeader.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/SelectField.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ThemeImageComponent/RewardsThemeImageComponent.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SelectField.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/InputStepperDescriptionRow.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx</t>
   </si>
   <si>
     <t>Jazzicon</t>
@@ -697,7 +697,7 @@
     <t>Maskicon</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGridItem.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGridItem.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/Keypad.stories.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/CollapsibleSectionHeader.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/SectionHeader/SectionHeader.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchResults/ExploreSearchResults.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/SelectField.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/SelectField.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardPointsAnimation/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralInfoSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralInfoSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep2.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep2.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep3.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep3.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep1.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep1.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicks.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictClaimButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SelectField.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyingVeriffKYC.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/components/DaimoPayModal/DaimoPayModal.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/InputStepperDescriptionRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/account-type-label/account-type-label.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/ViewMoreCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Perpetuals/components/PerpsViewMoreCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Perpetuals/components/PerpsMarketTileCard/PerpsMarketTileCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Perpetuals/components/PerpsMarketTileCard/PerpsMarketTileCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/SwapEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/CardEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/MusdDepositEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/BonusCodeEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabBar/PredictMarketDetailsTabBar.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsPositions/PredictMarketDetailsPositions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGridItem.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGridItem.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/Keypad.stories.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/NetworkDetailsView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/CollapsibleSectionHeader.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsFeedbackBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/SectionHeader/SectionHeader.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchResults/ExploreSearchResults.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/RpcEndpointSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/SelectField.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/SelectField.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/BlockExplorerSection.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworkDetailsView/components/NetworkFormFields.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardsEnvironmentToggle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardPointsAnimation/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep2.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep2.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep3.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep3.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep1.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep1.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralInfoSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralInfoSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicks.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictClaimButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyingVeriffKYC.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SelectField.tsx, repos/metamask-mobile/app/components/UI/Card/components/DaimoPayModal/DaimoPayModal.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/Cashback/Cashback.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/InputStepperDescriptionRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-item/highlighted-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/account-type-label/account-type-label.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/ViewMoreCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Perpetuals/components/PerpsViewMoreCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Perpetuals/components/PerpsMarketTileCard/PerpsMarketTileCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Perpetuals/components/PerpsMarketTileCard/PerpsMarketTileCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/BonusCodeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/SwapEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/MusdDepositEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/CardEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/BonusCodeEventDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabBar/PredictMarketDetailsTabBar.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsPositions/PredictMarketDetailsPositions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx</t>
